--- a/03_Outputs/Agroindustrial_Occidente/08_Educacion/educacion.xlsx
+++ b/03_Outputs/Agroindustrial_Occidente/08_Educacion/educacion.xlsx
@@ -3628,13 +3628,13 @@
         <v>2021</v>
       </c>
       <c r="F98" s="7">
-        <v>0.707047418431448</v>
+        <v>0.840377678716449</v>
       </c>
       <c r="G98" s="9">
-        <v>0.0173396704665876</v>
+        <v>0.0641520138915549</v>
       </c>
       <c r="H98" s="11">
-        <v>0.0227892744267992</v>
+        <v>0.0620288291108401</v>
       </c>
     </row>
     <row r="99">
@@ -3662,13 +3662,13 @@
         <v>2021</v>
       </c>
       <c r="F99" s="7">
-        <v>0.751725461200452</v>
+        <v>0.839551588466629</v>
       </c>
       <c r="G99" s="9">
-        <v>0.0449901180989826</v>
+        <v>0.0579854236957749</v>
       </c>
       <c r="H99" s="11">
-        <v>0.0279247119161082</v>
+        <v>0.0699376159957595</v>
       </c>
     </row>
     <row r="100">
@@ -3696,13 +3696,13 @@
         <v>2021</v>
       </c>
       <c r="F100" s="7">
-        <v>0.808399619674067</v>
+        <v>0.924418856993982</v>
       </c>
       <c r="G100" s="9">
-        <v>0.0340611041845194</v>
+        <v>0.0471531226376282</v>
       </c>
       <c r="H100" s="11">
-        <v>0.0537186135094694</v>
+        <v>0.0582136438740334</v>
       </c>
     </row>
     <row r="101">
